--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="369">
   <si>
     <t>Notes</t>
   </si>
@@ -960,6 +960,180 @@
   </si>
   <si>
     <t>Thu Nov 20 22:03:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:26:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:27:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:29:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 00:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:24:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:26:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:27:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 23:29:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:35:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:37:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:38:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 01:41:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:41:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:01:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:05:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:06:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 25 23:10:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 01:51:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:17:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:19:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:21:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 07:22:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:49:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:51:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 26 22:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:46:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:48:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:49:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:51:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 01:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:31:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:33:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 22:38:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 00:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:31:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:32:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 05 08:35:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:17:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:18:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:21:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 01:22:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:58:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 06:59:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:01:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:02:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 07:04:16 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1639,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>368</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -1761,7 +1935,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>367</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2021,7 +2195,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2140,7 +2314,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
@@ -2259,7 +2433,7 @@
         <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="C4" t="s">
         <v>127</v>

--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="374">
   <si>
     <t>Notes</t>
   </si>
@@ -1134,6 +1134,21 @@
   </si>
   <si>
     <t>Wed Mar 11 07:04:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:11:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:13:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:14:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 22 21:16:02 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1639,7 +1654,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -1935,7 +1950,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2195,7 +2210,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2314,7 +2329,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
@@ -2433,7 +2448,7 @@
         <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C4" t="s">
         <v>127</v>

--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="384">
   <si>
     <t>Notes</t>
   </si>
@@ -1149,6 +1149,36 @@
   </si>
   <si>
     <t>Wed Apr 22 21:16:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:10:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:14:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:15:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 09 00:17:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:27:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:28:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:30:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 17 00:31:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1684,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -1950,7 +1980,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2210,7 +2240,7 @@
         <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C2" t="s">
         <v>127</v>
@@ -2329,7 +2359,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C3" t="s">
         <v>127</v>
@@ -2448,7 +2478,7 @@
         <v>127</v>
       </c>
       <c r="B4" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C4" t="s">
         <v>127</v>

--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="389">
   <si>
     <t>Notes</t>
   </si>
@@ -1179,6 +1179,21 @@
   </si>
   <si>
     <t>Wed Jun 17 00:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:28:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:29:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:32:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:33:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:34:16 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:53" x14ac:dyDescent="0.3">
@@ -1680,13 +1695,13 @@
       </c>
     </row>
     <row ht="86.4" r="2" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1746,7 +1761,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1815,7 +1830,7 @@
       <c r="AV2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" t="s" s="0">
         <v>80</v>
       </c>
       <c r="AX2" s="1" t="s">
@@ -1841,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE003A9-015F-4019-B3A4-BC91F3755137}">
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:43" x14ac:dyDescent="0.3">
@@ -1976,13 +1991,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>387</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2042,7 +2057,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -2104,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C451C5-0490-4FE9-A49C-7BA5D775F32A}">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="43.2" r="1" spans="1:42" x14ac:dyDescent="0.3">
@@ -2236,13 +2251,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>384</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2302,7 +2317,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -2355,13 +2370,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>385</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2421,7 +2436,7 @@
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" t="s">
+      <c r="Z3" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA3" s="1" t="s">
@@ -2474,13 +2489,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -2540,7 +2555,7 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" t="s">
+      <c r="Z4" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA4" s="1" t="s">

--- a/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/VSP-Data-Prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="409">
   <si>
     <t>Notes</t>
   </si>
@@ -1179,6 +1179,81 @@
   </si>
   <si>
     <t>Wed Jun 17 00:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:50:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:51:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:52:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:54:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 30 22:55:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:19:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:20:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:21:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 02 20:22:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:16:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:18:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:20:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 17:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:46:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:47:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:48:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 16:51:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:44:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:46:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 08 06:49:10 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BA2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:53" x14ac:dyDescent="0.3">
@@ -1680,13 +1755,13 @@
       </c>
     </row>
     <row ht="86.4" r="2" spans="1:53" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>408</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1746,7 +1821,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -1815,7 +1890,7 @@
       <c r="AV2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AW2" t="s" s="0">
         <v>80</v>
       </c>
       <c r="AX2" s="1" t="s">
@@ -1841,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE003A9-015F-4019-B3A4-BC91F3755137}">
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:43" x14ac:dyDescent="0.3">
@@ -1976,13 +2051,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2042,7 +2117,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -2104,7 +2179,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C451C5-0490-4FE9-A49C-7BA5D775F32A}">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="43.2" r="1" spans="1:42" x14ac:dyDescent="0.3">
@@ -2236,13 +2311,13 @@
       </c>
     </row>
     <row ht="57.6" r="2" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>404</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -2302,7 +2377,7 @@
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" t="s">
+      <c r="Z2" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
@@ -2355,13 +2430,13 @@
       </c>
     </row>
     <row ht="57.6" r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>405</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2421,7 +2496,7 @@
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" t="s">
+      <c r="Z3" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA3" s="1" t="s">
@@ -2474,13 +2549,13 @@
       </c>
     </row>
     <row ht="57.6" r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="B4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s" s="0">
+        <v>406</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>127</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -2540,7 +2615,7 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" t="s">
+      <c r="Z4" t="s" s="0">
         <v>60</v>
       </c>
       <c r="AA4" s="1" t="s">
